--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0003T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>21.3718751557985</v>
+        <v>3.472929712817256</v>
       </c>
       <c r="D2" t="n">
-        <v>15.57305304824736</v>
+        <v>2.530621120340196</v>
       </c>
       <c r="E2" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F2" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>4.08901463712784</v>
+        <v>0.6644648785332741</v>
       </c>
       <c r="D3" t="n">
-        <v>4.732341946269409</v>
+        <v>0.7690055662687789</v>
       </c>
       <c r="E3" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F3" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.42894733012596</v>
+        <v>3.644703941145468</v>
       </c>
       <c r="D4" t="n">
-        <v>22.70655575670137</v>
+        <v>3.689815310463973</v>
       </c>
       <c r="E4" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F4" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.66109329338196</v>
+        <v>5.144927660174568</v>
       </c>
       <c r="D5" t="n">
-        <v>19.49790674269777</v>
+        <v>3.168409845688387</v>
       </c>
       <c r="E5" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F5" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>12.17099317223319</v>
+        <v>1.977786390487894</v>
       </c>
       <c r="D6" t="n">
-        <v>11.83679115314339</v>
+        <v>1.923478562385801</v>
       </c>
       <c r="E6" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F6" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>11.62097460432894</v>
+        <v>1.888408373203453</v>
       </c>
       <c r="D7" t="n">
-        <v>3.931167973090585</v>
+        <v>0.6388147956272201</v>
       </c>
       <c r="E7" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F7" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.77066844127914</v>
+        <v>1.42523362170786</v>
       </c>
       <c r="D8" t="n">
-        <v>9.134884271392599</v>
+        <v>1.484418694101297</v>
       </c>
       <c r="E8" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F8" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>24.44757304279119</v>
+        <v>3.972730619453569</v>
       </c>
       <c r="D9" t="n">
-        <v>10.56195647979486</v>
+        <v>1.716317927966664</v>
       </c>
       <c r="E9" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F9" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>29.7823227742319</v>
+        <v>4.839627450812684</v>
       </c>
       <c r="D10" t="n">
-        <v>16.4139006699834</v>
+        <v>2.667258858872303</v>
       </c>
       <c r="E10" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F10" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>25.3981000355291</v>
+        <v>4.127191255773479</v>
       </c>
       <c r="D11" t="n">
-        <v>16.0835252339348</v>
+        <v>2.613572850514406</v>
       </c>
       <c r="E11" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F11" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>10.57379118923866</v>
+        <v>1.718241068251283</v>
       </c>
       <c r="D12" t="n">
-        <v>15.91383046283955</v>
+        <v>2.585997450211427</v>
       </c>
       <c r="E12" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F12" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>24.10912660224624</v>
+        <v>3.917733072865014</v>
       </c>
       <c r="D13" t="n">
-        <v>20.28030689392133</v>
+        <v>3.295549870262216</v>
       </c>
       <c r="E13" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F13" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>12.4369894355822</v>
+        <v>2.021010783282107</v>
       </c>
       <c r="D14" t="n">
-        <v>8.664366432167531</v>
+        <v>1.407959545227224</v>
       </c>
       <c r="E14" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F14" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>19.86656204412722</v>
+        <v>3.228316332170674</v>
       </c>
       <c r="D15" t="n">
-        <v>12.63198658359054</v>
+        <v>2.052697819833462</v>
       </c>
       <c r="E15" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F15" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>30.63191135012345</v>
+        <v>4.977685594395061</v>
       </c>
       <c r="D16" t="n">
-        <v>27.65134605720868</v>
+        <v>4.49334373429641</v>
       </c>
       <c r="E16" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F16" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>16.29448371711039</v>
+        <v>2.647853604030438</v>
       </c>
       <c r="D17" t="n">
-        <v>15.87893304904812</v>
+        <v>2.580326620470319</v>
       </c>
       <c r="E17" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F17" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>9.96129626612699</v>
+        <v>1.618710643245636</v>
       </c>
       <c r="D18" t="n">
-        <v>11.00142596799398</v>
+        <v>1.787731719799022</v>
       </c>
       <c r="E18" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F18" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>12.96963289363332</v>
+        <v>2.107565345215415</v>
       </c>
       <c r="D19" t="n">
-        <v>16.38509008276545</v>
+        <v>2.662577138449385</v>
       </c>
       <c r="E19" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F19" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>23.92974512121327</v>
+        <v>3.888583582197157</v>
       </c>
       <c r="D20" t="n">
-        <v>24.47261304473545</v>
+        <v>3.976799619769511</v>
       </c>
       <c r="E20" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F20" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>26.59094228234013</v>
+        <v>4.321028120880272</v>
       </c>
       <c r="D21" t="n">
-        <v>26.16495970078716</v>
+        <v>4.251805951377914</v>
       </c>
       <c r="E21" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F21" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>30.27528623876132</v>
+        <v>4.919734013798715</v>
       </c>
       <c r="D22" t="n">
-        <v>24.66672081893726</v>
+        <v>4.008342133077305</v>
       </c>
       <c r="E22" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F22" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>29.45511671815497</v>
+        <v>4.786456466700183</v>
       </c>
       <c r="D23" t="n">
-        <v>31.6156172514648</v>
+        <v>5.137537803363029</v>
       </c>
       <c r="E23" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F23" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>34.98124826856964</v>
+        <v>5.684452843642568</v>
       </c>
       <c r="D24" t="n">
-        <v>34.56359045409631</v>
+        <v>5.61658344879065</v>
       </c>
       <c r="E24" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F24" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>20.07127346617251</v>
+        <v>3.261581938253034</v>
       </c>
       <c r="D25" t="n">
-        <v>19.45535478949865</v>
+        <v>3.161495153293531</v>
       </c>
       <c r="E25" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F25" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>39.9798471815391</v>
+        <v>6.496725167000104</v>
       </c>
       <c r="D26" t="n">
-        <v>39.63549545612238</v>
+        <v>6.440768011619888</v>
       </c>
       <c r="E26" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F26" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>13.37377285890336</v>
+        <v>2.173238089571796</v>
       </c>
       <c r="D27" t="n">
-        <v>2.936402142503026</v>
+        <v>0.4771653481567418</v>
       </c>
       <c r="E27" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F27" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>19.14574710358364</v>
+        <v>3.111183904332341</v>
       </c>
       <c r="D28" t="n">
-        <v>20.70651289560994</v>
+        <v>3.364808345536615</v>
       </c>
       <c r="E28" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F28" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>34.48964781094973</v>
+        <v>5.604567769279331</v>
       </c>
       <c r="D29" t="n">
-        <v>32.82536186644859</v>
+        <v>5.334121303297896</v>
       </c>
       <c r="E29" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F29" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>29.66836637014088</v>
+        <v>4.821109535147894</v>
       </c>
       <c r="D30" t="n">
-        <v>29.68125734266723</v>
+        <v>4.823204318183424</v>
       </c>
       <c r="E30" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F30" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>9.263453137438146</v>
+        <v>1.505311134833699</v>
       </c>
       <c r="D31" t="n">
-        <v>9.569132824714103</v>
+        <v>1.554984084016042</v>
       </c>
       <c r="E31" t="n">
-        <v>9.178003522551558</v>
+        <v>1.491425572414628</v>
       </c>
       <c r="F31" t="n">
-        <v>9.298632245271476</v>
+        <v>1.511027739856615</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
